--- a/artfynd/A 42444-2023 artfynd.xlsx
+++ b/artfynd/A 42444-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42444-2023 artfynd.xlsx
+++ b/artfynd/A 42444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112552152</v>
       </c>
       <c r="B2" t="n">
-        <v>77103</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112552866</v>
+        <v>112555965</v>
       </c>
       <c r="B3" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385353</v>
+        <v>385368</v>
       </c>
       <c r="R3" t="n">
-        <v>6953338</v>
+        <v>6953462</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,12 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112555965</v>
+        <v>112553825</v>
       </c>
       <c r="B4" t="n">
-        <v>77827</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,13 +907,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385368</v>
+        <v>385318</v>
       </c>
       <c r="R4" t="n">
-        <v>6953463</v>
+        <v>6953527</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,56 +969,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112553295</v>
+        <v>112553041</v>
       </c>
       <c r="B5" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385280</v>
+        <v>385353</v>
       </c>
       <c r="R5" t="n">
-        <v>6953501</v>
+        <v>6953339</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1060,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,59 +1067,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112555676</v>
+        <v>112565413</v>
       </c>
       <c r="B6" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Ö storbäcken, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385383</v>
+        <v>385296</v>
       </c>
       <c r="R6" t="n">
-        <v>6953559</v>
+        <v>6953368</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,6 +1149,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112553835</v>
+        <v>112555026</v>
       </c>
       <c r="B7" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,43 +1179,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385318</v>
+        <v>385522</v>
       </c>
       <c r="R7" t="n">
-        <v>6953527</v>
+        <v>6953733</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112554909</v>
+        <v>112555710</v>
       </c>
       <c r="B8" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,13 +1302,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385456</v>
+        <v>385383</v>
       </c>
       <c r="R8" t="n">
-        <v>6953861</v>
+        <v>6953558</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112553840</v>
+        <v>112555186</v>
       </c>
       <c r="B9" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,13 +1400,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385318</v>
+        <v>385557</v>
       </c>
       <c r="R9" t="n">
-        <v>6953527</v>
+        <v>6953699</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,56 +1462,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112551198</v>
+        <v>112555213</v>
       </c>
       <c r="B10" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385238</v>
+        <v>385557</v>
       </c>
       <c r="R10" t="n">
-        <v>6953248</v>
+        <v>6953707</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,19 +1531,9 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,19 +1560,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112555213</v>
+        <v>112555327</v>
       </c>
       <c r="B11" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1673,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385558</v>
+        <v>385463</v>
       </c>
       <c r="R11" t="n">
-        <v>6953707</v>
+        <v>6953681</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1706,9 +1629,19 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,51 +1668,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112551241</v>
+        <v>112556226</v>
       </c>
       <c r="B12" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385250</v>
+        <v>385535</v>
       </c>
       <c r="R12" t="n">
-        <v>6953258</v>
+        <v>6953420</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1838,15 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112554913</v>
+        <v>112550337</v>
       </c>
       <c r="B13" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,35 +1777,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385456</v>
+        <v>385220</v>
       </c>
       <c r="R13" t="n">
-        <v>6953861</v>
+        <v>6953207</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,9 +1835,19 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,27 +1862,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112550337</v>
+        <v>112550629</v>
       </c>
       <c r="B14" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,14 +1906,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385219</v>
+        <v>385198</v>
       </c>
       <c r="R14" t="n">
-        <v>6953207</v>
+        <v>6953235</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,19 +1943,9 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,27 +1960,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112555611</v>
+        <v>112551241</v>
       </c>
       <c r="B15" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2095,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385416</v>
+        <v>385251</v>
       </c>
       <c r="R15" t="n">
-        <v>6953575</v>
+        <v>6953258</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2157,15 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112555859</v>
+        <v>112552809</v>
       </c>
       <c r="B16" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,40 +2081,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385411</v>
+        <v>385265</v>
       </c>
       <c r="R16" t="n">
-        <v>6953503</v>
+        <v>6953309</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2233,12 +2136,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,27 +2156,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112555026</v>
+        <v>112552909</v>
       </c>
       <c r="B17" t="n">
-        <v>88745</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,21 +2179,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385522</v>
+        <v>385353</v>
       </c>
       <c r="R17" t="n">
-        <v>6953734</v>
+        <v>6953339</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2336,12 +2234,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,15 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112552809</v>
+        <v>112553585</v>
       </c>
       <c r="B18" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385265</v>
+        <v>385281</v>
       </c>
       <c r="R18" t="n">
-        <v>6953309</v>
+        <v>6953539</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2439,12 +2332,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,15 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112555186</v>
+        <v>112554582</v>
       </c>
       <c r="B19" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,21 +2375,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385557</v>
+        <v>385354</v>
       </c>
       <c r="R19" t="n">
-        <v>6953699</v>
+        <v>6953755</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2574,37 +2462,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112555960</v>
+        <v>112555707</v>
       </c>
       <c r="B20" t="n">
-        <v>78743</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2615,13 +2498,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385380</v>
+        <v>385383</v>
       </c>
       <c r="R20" t="n">
-        <v>6953452</v>
+        <v>6953558</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2677,37 +2560,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112552909</v>
+        <v>112552865</v>
       </c>
       <c r="B21" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6443</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,7 +2599,7 @@
         <v>385353</v>
       </c>
       <c r="R21" t="n">
-        <v>6953338</v>
+        <v>6953339</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2780,54 +2658,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112554708</v>
+        <v>112565409</v>
       </c>
       <c r="B22" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Ö storbäcken, Mittådalen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385378</v>
+        <v>385394</v>
       </c>
       <c r="R22" t="n">
-        <v>6953837</v>
+        <v>6953668</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2865,55 +2740,51 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112554717</v>
+        <v>112550547</v>
       </c>
       <c r="B23" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2924,10 +2795,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385378</v>
+        <v>385220</v>
       </c>
       <c r="R23" t="n">
-        <v>6953837</v>
+        <v>6953207</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2957,9 +2828,19 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2986,15 +2867,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112550547</v>
+        <v>112554111</v>
       </c>
       <c r="B24" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,14 +2899,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385219</v>
+        <v>385310</v>
       </c>
       <c r="R24" t="n">
-        <v>6953207</v>
+        <v>6953713</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3060,19 +2936,9 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3087,68 +2953,58 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112553047</v>
+        <v>112555960</v>
       </c>
       <c r="B25" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385361</v>
+        <v>385380</v>
       </c>
       <c r="R25" t="n">
-        <v>6953401</v>
+        <v>6953451</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3178,19 +3034,9 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3205,27 +3051,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112554111</v>
+        <v>112550623</v>
       </c>
       <c r="B26" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3099,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385311</v>
+        <v>385198</v>
       </c>
       <c r="R26" t="n">
-        <v>6953713</v>
+        <v>6953235</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3320,15 +3161,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112553585</v>
+        <v>112554588</v>
       </c>
       <c r="B27" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,21 +3172,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3361,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385281</v>
+        <v>385354</v>
       </c>
       <c r="R27" t="n">
-        <v>6953539</v>
+        <v>6953755</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3423,51 +3259,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112554720</v>
+        <v>112551198</v>
       </c>
       <c r="B28" t="n">
-        <v>78836</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385378</v>
+        <v>385238</v>
       </c>
       <c r="R28" t="n">
-        <v>6953837</v>
+        <v>6953248</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3497,9 +3333,19 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3526,15 +3372,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112554588</v>
+        <v>112553047</v>
       </c>
       <c r="B29" t="n">
-        <v>76726</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,35 +3383,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385354</v>
+        <v>385360</v>
       </c>
       <c r="R29" t="n">
-        <v>6953754</v>
+        <v>6953400</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3600,9 +3446,19 @@
           <t>2023-10-06</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,27 +3473,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112553202</v>
+        <v>112553286</v>
       </c>
       <c r="B30" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,38 +3496,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385320</v>
+        <v>385276</v>
       </c>
       <c r="R30" t="n">
-        <v>6953464</v>
+        <v>6953386</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3720,63 +3576,63 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112553041</v>
+        <v>112553295</v>
       </c>
       <c r="B31" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385353</v>
+        <v>385280</v>
       </c>
       <c r="R31" t="n">
-        <v>6953338</v>
+        <v>6953501</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3803,12 +3659,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,15 +3691,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112553825</v>
+        <v>112553835</v>
       </c>
       <c r="B32" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,25 +3702,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
@@ -3938,54 +3794,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112552865</v>
+        <v>112555676</v>
       </c>
       <c r="B33" t="n">
-        <v>77102</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6443</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385353</v>
+        <v>385383</v>
       </c>
       <c r="R33" t="n">
-        <v>6953338</v>
+        <v>6953558</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4009,12 +3865,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4041,15 +3897,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112554833</v>
+        <v>112555859</v>
       </c>
       <c r="B34" t="n">
-        <v>56658</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,38 +3908,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385449</v>
+        <v>385411</v>
       </c>
       <c r="R34" t="n">
-        <v>6953873</v>
+        <v>6953503</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4132,27 +3988,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112555710</v>
+        <v>112552866</v>
       </c>
       <c r="B35" t="n">
-        <v>88745</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385383</v>
+        <v>385353</v>
       </c>
       <c r="R35" t="n">
-        <v>6953559</v>
+        <v>6953339</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,12 +4066,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4247,15 +4098,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112553286</v>
+        <v>112553202</v>
       </c>
       <c r="B36" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4263,43 +4109,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385276</v>
+        <v>385320</v>
       </c>
       <c r="R36" t="n">
-        <v>6953386</v>
+        <v>6953464</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4343,27 +4184,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112554582</v>
+        <v>112553442</v>
       </c>
       <c r="B37" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,21 +4207,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,10 +4232,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385354</v>
+        <v>385269</v>
       </c>
       <c r="R37" t="n">
-        <v>6953754</v>
+        <v>6953456</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4458,15 +4294,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112555327</v>
+        <v>112553582</v>
       </c>
       <c r="B38" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4474,35 +4305,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öster-Storbäcken, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385463</v>
+        <v>385281</v>
       </c>
       <c r="R38" t="n">
-        <v>6953681</v>
+        <v>6953539</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4532,19 +4363,9 @@
           <t>2023-10-06</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,27 +4380,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112555844</v>
+        <v>112555611</v>
       </c>
       <c r="B39" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4612,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385368</v>
+        <v>385415</v>
       </c>
       <c r="R39" t="n">
-        <v>6953463</v>
+        <v>6953576</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4674,15 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112553442</v>
+        <v>112555844</v>
       </c>
       <c r="B40" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385269</v>
+        <v>385368</v>
       </c>
       <c r="R40" t="n">
-        <v>6953457</v>
+        <v>6953462</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,15 +4588,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112553582</v>
+        <v>112556390</v>
       </c>
       <c r="B41" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4814,14 +4620,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385281</v>
+        <v>385551</v>
       </c>
       <c r="R41" t="n">
-        <v>6953539</v>
+        <v>6953318</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4880,56 +4686,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112565409</v>
+        <v>112554909</v>
       </c>
       <c r="B42" t="n">
-        <v>77212</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6443</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ö storbäcken, Mittådalen, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385394</v>
+        <v>385456</v>
       </c>
       <c r="R42" t="n">
-        <v>6953668</v>
+        <v>6953861</v>
       </c>
       <c r="S42" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4967,7 +4766,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4986,54 +4784,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112555707</v>
+        <v>112554708</v>
       </c>
       <c r="B43" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Östervallen, Hjd</t>
+          <t>Öster-Storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385383</v>
+        <v>385378</v>
       </c>
       <c r="R43" t="n">
-        <v>6953559</v>
+        <v>6953837</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5077,27 +4870,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112565413</v>
+        <v>112554913</v>
       </c>
       <c r="B44" t="n">
-        <v>89924</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5105,40 +4893,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ö storbäcken, Mittådalen, Hjd</t>
+          <t>Östervallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385296</v>
+        <v>385456</v>
       </c>
       <c r="R44" t="n">
-        <v>6953368</v>
+        <v>6953861</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5176,7 +4962,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5192,6 +4977,300 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112554720</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Öster-Storbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>385378</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6953837</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112554717</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Öster-Storbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>385378</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6953837</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>112554833</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Östervallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>385449</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6953873</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42444-2023 artfynd.xlsx
+++ b/artfynd/A 42444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553041</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112565413</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555710</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554913</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555186</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555213</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112556226</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550337</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550629</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551241</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2459,6 +2549,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552809</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552909</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553585</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2753,6 +2858,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554582</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2851,6 +2961,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555707</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2949,6 +3064,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552865</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112565409</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3158,6 +3283,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550547</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3256,6 +3386,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554111</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3354,6 +3489,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555960</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3452,6 +3592,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554720</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3550,6 +3695,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554717</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3648,6 +3798,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550623</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3746,6 +3901,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554588</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3859,6 +4019,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551198</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3972,6 +4137,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553047</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4075,6 +4245,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553286</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4178,6 +4353,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553295</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4281,6 +4461,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553835</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4384,6 +4569,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555676</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4487,6 +4677,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555859</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4585,6 +4780,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112554833</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4683,6 +4883,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552866</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4781,6 +4986,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553202</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4879,6 +5089,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553442</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4977,6 +5192,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112553582</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5075,6 +5295,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555611</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5173,6 +5398,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555844</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5271,8 +5501,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112556390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>